--- a/bills/JXZFSP01/-4779823523/5476718c6a9c472b26ad561409fbaeb927d48f653cbdf0e46edc2daa236da9d3/bill-all.xlsx
+++ b/bills/JXZFSP01/-4779823523/5476718c6a9c472b26ad561409fbaeb927d48f653cbdf0e46edc2daa236da9d3/bill-all.xlsx
@@ -244,83 +244,110 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>08/30 16:06:08</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>13095</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>07/30 18:48:54</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>7647</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>175000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20742.3</t>
+          <t>175000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7647</t>
+          <t>20742.3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>20742</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>13095.3</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0.3</t>
         </is>
       </c>
     </row>
